--- a/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887930A6-D78F-4BDC-8F2E-5D354A3022E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFCCD7E2-04E8-4F48-8624-0EBCD5791927}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C220E4-8F62-4662-82F5-E862B6011EC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA9C322-F997-413A-B20A-01288CA536FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DFF80CC-050D-497A-817E-675FDBDAF31B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DAE03F-E96D-4345-8104-3A6D9F373628}"/>
 </file>